--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/145.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/145.xlsx
@@ -426,13 +426,13 @@
         <v>-10.29893648994398</v>
       </c>
       <c r="E2">
-        <v>-29.15472982922406</v>
+        <v>-30.26723551021443</v>
       </c>
       <c r="F2">
-        <v>-3.963995791905413</v>
+        <v>-4.117440084497785</v>
       </c>
       <c r="G2">
-        <v>-19.61794640910777</v>
+        <v>-18.40746364067372</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.10472040388108</v>
       </c>
       <c r="E3">
-        <v>-29.00513621885468</v>
+        <v>-30.91066826806828</v>
       </c>
       <c r="F3">
-        <v>-3.839318214110059</v>
+        <v>-3.890950354326552</v>
       </c>
       <c r="G3">
-        <v>-19.06440995275947</v>
+        <v>-18.58567196232546</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.93128585656209</v>
       </c>
       <c r="E4">
-        <v>-28.91531846538654</v>
+        <v>-30.70572085566614</v>
       </c>
       <c r="F4">
-        <v>-3.899195923454019</v>
+        <v>-3.753372610967402</v>
       </c>
       <c r="G4">
-        <v>-17.92788642694551</v>
+        <v>-17.94780266890977</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.68170802401388</v>
       </c>
       <c r="E5">
-        <v>-29.08124175302759</v>
+        <v>-31.27493871724528</v>
       </c>
       <c r="F5">
-        <v>-3.947372943233435</v>
+        <v>-3.804320519709183</v>
       </c>
       <c r="G5">
-        <v>-17.93848182794395</v>
+        <v>-17.89279464422923</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.33590949069823</v>
       </c>
       <c r="E6">
-        <v>-30.45887373750803</v>
+        <v>-31.46161147278947</v>
       </c>
       <c r="F6">
-        <v>-4.215276073340226</v>
+        <v>-3.860075444489409</v>
       </c>
       <c r="G6">
-        <v>-17.8503849005984</v>
+        <v>-17.7500472311214</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.85243867252666</v>
       </c>
       <c r="E7">
-        <v>-30.13563805555153</v>
+        <v>-31.55019974556452</v>
       </c>
       <c r="F7">
-        <v>-3.843764890328287</v>
+        <v>-3.675190467123782</v>
       </c>
       <c r="G7">
-        <v>-17.37511801716232</v>
+        <v>-17.29747248208426</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.20812372713782</v>
       </c>
       <c r="E8">
-        <v>-30.44589965947605</v>
+        <v>-32.20586617595009</v>
       </c>
       <c r="F8">
-        <v>-3.797484831901281</v>
+        <v>-3.806489185569712</v>
       </c>
       <c r="G8">
-        <v>-17.80971153810292</v>
+        <v>-16.94971953645705</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.37696875293948</v>
       </c>
       <c r="E9">
-        <v>-31.32704107494054</v>
+        <v>-32.04568952182478</v>
       </c>
       <c r="F9">
-        <v>-3.681883675738402</v>
+        <v>-3.823018428725173</v>
       </c>
       <c r="G9">
-        <v>-17.26368836485599</v>
+        <v>-16.83285231310247</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.34883748363691</v>
       </c>
       <c r="E10">
-        <v>-32.57239180518292</v>
+        <v>-32.80846115520277</v>
       </c>
       <c r="F10">
-        <v>-3.736963481085346</v>
+        <v>-3.87217209367249</v>
       </c>
       <c r="G10">
-        <v>-16.97226104103395</v>
+        <v>-16.32348350006636</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.11339871061355</v>
       </c>
       <c r="E11">
-        <v>-32.09344680870968</v>
+        <v>-33.51790321442943</v>
       </c>
       <c r="F11">
-        <v>-3.576076307378821</v>
+        <v>-3.91523974331144</v>
       </c>
       <c r="G11">
-        <v>-17.44031259046719</v>
+        <v>-16.28269095793146</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.67702671439872</v>
       </c>
       <c r="E12">
-        <v>-33.52351172948793</v>
+        <v>-34.04508778026938</v>
       </c>
       <c r="F12">
-        <v>-3.671963147722475</v>
+        <v>-3.890439251639025</v>
       </c>
       <c r="G12">
-        <v>-16.2526792073452</v>
+        <v>-15.73826843345277</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.04877152169625</v>
       </c>
       <c r="E13">
-        <v>-33.34305204028227</v>
+        <v>-34.6681333481407</v>
       </c>
       <c r="F13">
-        <v>-3.052279717771027</v>
+        <v>-3.933045500634615</v>
       </c>
       <c r="G13">
-        <v>-15.70153462014902</v>
+        <v>-15.61634104124141</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.26108921157285</v>
       </c>
       <c r="E14">
-        <v>-33.68821685762091</v>
+        <v>-34.90783227007771</v>
       </c>
       <c r="F14">
-        <v>-3.468743914630686</v>
+        <v>-3.972073202450111</v>
       </c>
       <c r="G14">
-        <v>-16.05359458552281</v>
+        <v>-15.15067308459645</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.34597338779836</v>
       </c>
       <c r="E15">
-        <v>-35.18982487500934</v>
+        <v>-35.42368206547645</v>
       </c>
       <c r="F15">
-        <v>-3.448990665543529</v>
+        <v>-3.841735390191428</v>
       </c>
       <c r="G15">
-        <v>-15.61566072413309</v>
+        <v>-15.29925698949002</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.34557147125066</v>
       </c>
       <c r="E16">
-        <v>-35.08092186783588</v>
+        <v>-35.7742199172252</v>
       </c>
       <c r="F16">
-        <v>-2.782422468961032</v>
+        <v>-3.466284491811775</v>
       </c>
       <c r="G16">
-        <v>-14.89260612817364</v>
+        <v>-14.48683918251625</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.298939569300755</v>
       </c>
       <c r="E17">
-        <v>-34.86064330668077</v>
+        <v>-36.50433446029687</v>
       </c>
       <c r="F17">
-        <v>-3.207509142116431</v>
+        <v>-3.395768888281064</v>
       </c>
       <c r="G17">
-        <v>-13.71739722246053</v>
+        <v>-14.51270944063289</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.251494205724946</v>
       </c>
       <c r="E18">
-        <v>-36.52369595091666</v>
+        <v>-36.66651043569656</v>
       </c>
       <c r="F18">
-        <v>-3.076591472675789</v>
+        <v>-3.469235136500546</v>
       </c>
       <c r="G18">
-        <v>-15.12979016333473</v>
+        <v>-14.19494507177317</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.240076597262656</v>
       </c>
       <c r="E19">
-        <v>-36.12080893963925</v>
+        <v>-37.41960698435716</v>
       </c>
       <c r="F19">
-        <v>-2.763476049724201</v>
+        <v>-3.330845593086653</v>
       </c>
       <c r="G19">
-        <v>-14.71976089029553</v>
+        <v>-14.03425450184249</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.289315805739161</v>
       </c>
       <c r="E20">
-        <v>-37.24171041143984</v>
+        <v>-38.11983133474121</v>
       </c>
       <c r="F20">
-        <v>-2.526316947404911</v>
+        <v>-3.006765899191611</v>
       </c>
       <c r="G20">
-        <v>-14.50947503764102</v>
+        <v>-14.05963479921931</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.413992139666012</v>
       </c>
       <c r="E21">
-        <v>-38.20292656854495</v>
+        <v>-38.29232317393037</v>
       </c>
       <c r="F21">
-        <v>-2.562399803103455</v>
+        <v>-3.057350983010965</v>
       </c>
       <c r="G21">
-        <v>-14.38273411221556</v>
+        <v>-14.31381683045178</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.622592128334909</v>
       </c>
       <c r="E22">
-        <v>-38.40806644109242</v>
+        <v>-38.89423208937089</v>
       </c>
       <c r="F22">
-        <v>-2.720531826828269</v>
+        <v>-2.890459802368949</v>
       </c>
       <c r="G22">
-        <v>-13.77179776203461</v>
+        <v>-14.3936291175853</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.928149233996762</v>
       </c>
       <c r="E23">
-        <v>-38.8869163396115</v>
+        <v>-39.25089470221501</v>
       </c>
       <c r="F23">
-        <v>-2.270668684655136</v>
+        <v>-2.965119728015865</v>
       </c>
       <c r="G23">
-        <v>-14.41977746152724</v>
+        <v>-13.86371505893247</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.331926685244864</v>
       </c>
       <c r="E24">
-        <v>-38.76620533646304</v>
+        <v>-39.5780248718181</v>
       </c>
       <c r="F24">
-        <v>-1.968383337127749</v>
+        <v>-2.613381674908751</v>
       </c>
       <c r="G24">
-        <v>-13.76606058661505</v>
+        <v>-13.74169662671878</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.835735183058925</v>
       </c>
       <c r="E25">
-        <v>-39.69759696375363</v>
+        <v>-39.82201678711438</v>
       </c>
       <c r="F25">
-        <v>-2.350830626591447</v>
+        <v>-2.562419683921122</v>
       </c>
       <c r="G25">
-        <v>-15.05173246533702</v>
+        <v>-13.98894637559202</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.437328125677602</v>
       </c>
       <c r="E26">
-        <v>-39.75122315295247</v>
+        <v>-39.90750079095717</v>
       </c>
       <c r="F26">
-        <v>-1.85099207900742</v>
+        <v>-2.395005803447939</v>
       </c>
       <c r="G26">
-        <v>-14.19561711251765</v>
+        <v>-14.20235903850837</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.144827791693185</v>
       </c>
       <c r="E27">
-        <v>-40.2514746196318</v>
+        <v>-39.68295414304983</v>
       </c>
       <c r="F27">
-        <v>-2.165048527328588</v>
+        <v>-2.326574372302672</v>
       </c>
       <c r="G27">
-        <v>-13.98750794355521</v>
+        <v>-14.54009261806097</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.95678108970837</v>
       </c>
       <c r="E28">
-        <v>-39.87795249805712</v>
+        <v>-39.70682825801827</v>
       </c>
       <c r="F28">
-        <v>-2.148841519092816</v>
+        <v>-2.465465906362662</v>
       </c>
       <c r="G28">
-        <v>-14.56011810802802</v>
+        <v>-14.27116872754212</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.871901076234494</v>
       </c>
       <c r="E29">
-        <v>-39.21271513785634</v>
+        <v>-39.88220473515032</v>
       </c>
       <c r="F29">
-        <v>-2.266327211097064</v>
+        <v>-2.470816331417344</v>
       </c>
       <c r="G29">
-        <v>-14.18484459733286</v>
+        <v>-14.21150111001507</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.885710174891925</v>
       </c>
       <c r="E30">
-        <v>-39.25235739931949</v>
+        <v>-39.43917959450592</v>
       </c>
       <c r="F30">
-        <v>-2.716877069847118</v>
+        <v>-2.603793322221346</v>
       </c>
       <c r="G30">
-        <v>-14.01415949041911</v>
+        <v>-14.08276061508389</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.993729697154346</v>
       </c>
       <c r="E31">
-        <v>-39.30321669089963</v>
+        <v>-39.41706026321546</v>
       </c>
       <c r="F31">
-        <v>-2.268396472869257</v>
+        <v>-2.709051482992871</v>
       </c>
       <c r="G31">
-        <v>-14.19541185869421</v>
+        <v>-14.54879769755648</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.187313364856811</v>
       </c>
       <c r="E32">
-        <v>-39.37418693554784</v>
+        <v>-39.69430476315006</v>
       </c>
       <c r="F32">
-        <v>-2.025084257481972</v>
+        <v>-2.480499117988668</v>
       </c>
       <c r="G32">
-        <v>-14.56354617793393</v>
+        <v>-14.52260631652254</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.453043680643592</v>
       </c>
       <c r="E33">
-        <v>-39.2897376880158</v>
+        <v>-38.77871977438323</v>
       </c>
       <c r="F33">
-        <v>-2.477544331462882</v>
+        <v>-2.528274379577726</v>
       </c>
       <c r="G33">
-        <v>-14.14439800720681</v>
+        <v>-14.59619312276946</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.780247722597926</v>
       </c>
       <c r="E34">
-        <v>-37.8621249359127</v>
+        <v>-38.78491472682573</v>
       </c>
       <c r="F34">
-        <v>-2.132223640625255</v>
+        <v>-2.602943417266074</v>
       </c>
       <c r="G34">
-        <v>-14.38269604094186</v>
+        <v>-14.5067123873885</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.15610649248349</v>
       </c>
       <c r="E35">
-        <v>-37.07039371125566</v>
+        <v>-38.17468474039612</v>
       </c>
       <c r="F35">
-        <v>-2.537302755900838</v>
+        <v>-2.53049771768684</v>
       </c>
       <c r="G35">
-        <v>-14.14357368136753</v>
+        <v>-14.99018114739812</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.570661189361562</v>
       </c>
       <c r="E36">
-        <v>-38.70582039980776</v>
+        <v>-38.59684946552418</v>
       </c>
       <c r="F36">
-        <v>-2.215831590957212</v>
+        <v>-2.737138108152191</v>
       </c>
       <c r="G36">
-        <v>-13.85926403045492</v>
+        <v>-14.71024638241566</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.007441166956643</v>
       </c>
       <c r="E37">
-        <v>-37.08945179411694</v>
+        <v>-37.73972934043339</v>
       </c>
       <c r="F37">
-        <v>-2.660807365453828</v>
+        <v>-2.743432043678661</v>
       </c>
       <c r="G37">
-        <v>-14.56896057516341</v>
+        <v>-14.72000421539266</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.458404557490447</v>
       </c>
       <c r="E38">
-        <v>-36.74297371931608</v>
+        <v>-37.54351735439204</v>
       </c>
       <c r="F38">
-        <v>-2.135914017404727</v>
+        <v>-2.745298355437169</v>
       </c>
       <c r="G38">
-        <v>-14.89921397707003</v>
+        <v>-14.80555698849128</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.913023007815527</v>
       </c>
       <c r="E39">
-        <v>-35.29645911670496</v>
+        <v>-36.68116684182239</v>
       </c>
       <c r="F39">
-        <v>-2.527846941997882</v>
+        <v>-2.575810242987376</v>
       </c>
       <c r="G39">
-        <v>-14.34913869608304</v>
+        <v>-15.02032200926042</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.362222899430859</v>
       </c>
       <c r="E40">
-        <v>-36.09118366268107</v>
+        <v>-35.99631213222037</v>
       </c>
       <c r="F40">
-        <v>-2.395545898994564</v>
+        <v>-2.467990770206395</v>
       </c>
       <c r="G40">
-        <v>-14.18161847070484</v>
+        <v>-15.05634902109153</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.79267813466989</v>
       </c>
       <c r="E41">
-        <v>-35.00651224717885</v>
+        <v>-36.09816204112689</v>
       </c>
       <c r="F41">
-        <v>-2.348594034603888</v>
+        <v>-2.569697719922118</v>
       </c>
       <c r="G41">
-        <v>-14.62421358021385</v>
+        <v>-15.01676979389678</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.194822021626008</v>
       </c>
       <c r="E42">
-        <v>-35.5316318288713</v>
+        <v>-35.24581945611418</v>
       </c>
       <c r="F42">
-        <v>-1.949238109714247</v>
+        <v>-2.524077870315144</v>
       </c>
       <c r="G42">
-        <v>-13.76365050946246</v>
+        <v>-15.44528184268173</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.56197077660792</v>
       </c>
       <c r="E43">
-        <v>-34.16968194987942</v>
+        <v>-34.69338411920747</v>
       </c>
       <c r="F43">
-        <v>-2.233073230079081</v>
+        <v>-2.376471911177703</v>
       </c>
       <c r="G43">
-        <v>-14.74841200666515</v>
+        <v>-14.91084392354949</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.88848165574082</v>
       </c>
       <c r="E44">
-        <v>-33.70467559640178</v>
+        <v>-33.76996713464438</v>
       </c>
       <c r="F44">
-        <v>-2.519467177351162</v>
+        <v>-2.362279492465539</v>
       </c>
       <c r="G44">
-        <v>-14.3579066759438</v>
+        <v>-14.83574916380943</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.171073103745672</v>
       </c>
       <c r="E45">
-        <v>-33.87070756741901</v>
+        <v>-33.72419331937485</v>
       </c>
       <c r="F45">
-        <v>-2.027971117880729</v>
+        <v>-2.263003801077032</v>
       </c>
       <c r="G45">
-        <v>-14.50466978079077</v>
+        <v>-15.06965906943218</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.406205166045745</v>
       </c>
       <c r="E46">
-        <v>-34.37041335298042</v>
+        <v>-33.58990595115139</v>
       </c>
       <c r="F46">
-        <v>-1.839293046177682</v>
+        <v>-2.383904851883023</v>
       </c>
       <c r="G46">
-        <v>-15.06363056600516</v>
+        <v>-15.51206547784545</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.600919543372684</v>
       </c>
       <c r="E47">
-        <v>-32.55746595485364</v>
+        <v>-32.59801164688131</v>
       </c>
       <c r="F47">
-        <v>-2.169756139278697</v>
+        <v>-2.109812988909917</v>
       </c>
       <c r="G47">
-        <v>-14.95496356395136</v>
+        <v>-15.19325828714087</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.761514091828685</v>
       </c>
       <c r="E48">
-        <v>-31.88344335507797</v>
+        <v>-32.45399258801537</v>
       </c>
       <c r="F48">
-        <v>-1.884227007575139</v>
+        <v>-2.280008527121701</v>
       </c>
       <c r="G48">
-        <v>-14.09260948806322</v>
+        <v>-14.86968391085973</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.900841283226873</v>
       </c>
       <c r="E49">
-        <v>-30.53133837857877</v>
+        <v>-31.95500230134718</v>
       </c>
       <c r="F49">
-        <v>-1.988956669943678</v>
+        <v>-2.289592737972091</v>
       </c>
       <c r="G49">
-        <v>-14.94505841169786</v>
+        <v>-15.36214245728125</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.024613944461779</v>
       </c>
       <c r="E50">
-        <v>-29.95127482175126</v>
+        <v>-31.69426182493354</v>
       </c>
       <c r="F50">
-        <v>-2.175388209250332</v>
+        <v>-2.191894258118515</v>
       </c>
       <c r="G50">
-        <v>-15.12335446280638</v>
+        <v>-15.526568977853</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.14856301794407</v>
       </c>
       <c r="E51">
-        <v>-30.22610111656576</v>
+        <v>-30.64380529479627</v>
       </c>
       <c r="F51">
-        <v>-1.78307175054968</v>
+        <v>-2.245898014209223</v>
       </c>
       <c r="G51">
-        <v>-14.72797931959677</v>
+        <v>-15.33474934821655</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.284915920087238</v>
       </c>
       <c r="E52">
-        <v>-29.91848414146171</v>
+        <v>-30.25454446180794</v>
       </c>
       <c r="F52">
-        <v>-1.962191290791823</v>
+        <v>-2.181363223326724</v>
       </c>
       <c r="G52">
-        <v>-15.67330063251734</v>
+        <v>-15.0439874440479</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.446711061359334</v>
       </c>
       <c r="E53">
-        <v>-30.01295943044673</v>
+        <v>-30.16662187471201</v>
       </c>
       <c r="F53">
-        <v>-1.918366513346715</v>
+        <v>-2.072744376002042</v>
       </c>
       <c r="G53">
-        <v>-15.50803654392416</v>
+        <v>-15.57990848758173</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.641297974870934</v>
       </c>
       <c r="E54">
-        <v>-29.72183289344163</v>
+        <v>-30.34625285317427</v>
       </c>
       <c r="F54">
-        <v>-1.895165599129106</v>
+        <v>-2.268408070012896</v>
       </c>
       <c r="G54">
-        <v>-15.36731683995913</v>
+        <v>-15.44702650018093</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.871678197886869</v>
       </c>
       <c r="E55">
-        <v>-30.03304547690776</v>
+        <v>-29.65481600660211</v>
       </c>
       <c r="F55">
-        <v>-1.875608673116413</v>
+        <v>-2.177923013502898</v>
       </c>
       <c r="G55">
-        <v>-15.89217735084626</v>
+        <v>-15.48985833836802</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.142720037617893</v>
       </c>
       <c r="E56">
-        <v>-28.0588753471599</v>
+        <v>-29.62122831488722</v>
       </c>
       <c r="F56">
-        <v>-1.931873043849361</v>
+        <v>-2.070579851978527</v>
       </c>
       <c r="G56">
-        <v>-15.89607551821875</v>
+        <v>-15.67525219911274</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.451939017996432</v>
       </c>
       <c r="E57">
-        <v>-29.48671452296338</v>
+        <v>-28.84767212065996</v>
       </c>
       <c r="F57">
-        <v>-2.09314292329598</v>
+        <v>-2.352900716731043</v>
       </c>
       <c r="G57">
-        <v>-15.32114797186845</v>
+        <v>-15.67293150668972</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.79962291061929</v>
       </c>
       <c r="E58">
-        <v>-28.32288538180708</v>
+        <v>-28.48634517958795</v>
       </c>
       <c r="F58">
-        <v>-2.164634343627188</v>
+        <v>-2.231158044643808</v>
       </c>
       <c r="G58">
-        <v>-15.76130486458779</v>
+        <v>-15.82407280801237</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.17120342318818</v>
       </c>
       <c r="E59">
-        <v>-26.89781083938528</v>
+        <v>-28.63516442090202</v>
       </c>
       <c r="F59">
-        <v>-2.514574839470228</v>
+        <v>-2.359936041083019</v>
       </c>
       <c r="G59">
-        <v>-15.35765666807553</v>
+        <v>-15.49630065998744</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.56321095612777</v>
       </c>
       <c r="E60">
-        <v>-27.49186511665949</v>
+        <v>-28.469254718683</v>
       </c>
       <c r="F60">
-        <v>-2.413127168751581</v>
+        <v>-2.348714147877295</v>
       </c>
       <c r="G60">
-        <v>-16.01773475624143</v>
+        <v>-15.50644417151977</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.96378135864958</v>
       </c>
       <c r="E61">
-        <v>-27.30890570980159</v>
+        <v>-27.89605859268812</v>
       </c>
       <c r="F61">
-        <v>-2.769879329747841</v>
+        <v>-2.412417257887382</v>
       </c>
       <c r="G61">
-        <v>-15.12758865055111</v>
+        <v>-15.64022662730726</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.36598538152959</v>
       </c>
       <c r="E62">
-        <v>-26.34344410831429</v>
+        <v>-28.33598172863726</v>
       </c>
       <c r="F62">
-        <v>-2.228421947112361</v>
+        <v>-2.239253679271368</v>
       </c>
       <c r="G62">
-        <v>-15.62628095422308</v>
+        <v>-15.35249883812535</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.75278635441382</v>
       </c>
       <c r="E63">
-        <v>-26.48072932633082</v>
+        <v>-27.93608124596791</v>
       </c>
       <c r="F63">
-        <v>-2.520104191883915</v>
+        <v>-2.479914290602291</v>
       </c>
       <c r="G63">
-        <v>-15.57775001189013</v>
+        <v>-15.30471607908428</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.1124396919394</v>
       </c>
       <c r="E64">
-        <v>-27.44203378867909</v>
+        <v>-27.66357126560833</v>
       </c>
       <c r="F64">
-        <v>-2.208551069854007</v>
+        <v>-2.414619058444023</v>
       </c>
       <c r="G64">
-        <v>-15.19876869019098</v>
+        <v>-15.74141014116954</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.43297878540738</v>
       </c>
       <c r="E65">
-        <v>-26.49912398774998</v>
+        <v>-27.41765248462179</v>
       </c>
       <c r="F65">
-        <v>-2.229403562484679</v>
+        <v>-2.507189944074271</v>
       </c>
       <c r="G65">
-        <v>-15.96177329444559</v>
+        <v>-15.35094950281297</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.70224941399332</v>
       </c>
       <c r="E66">
-        <v>-27.94280150139529</v>
+        <v>-27.60438411032808</v>
       </c>
       <c r="F66">
-        <v>-2.160381505381216</v>
+        <v>-2.433835525454166</v>
       </c>
       <c r="G66">
-        <v>-15.47606329510588</v>
+        <v>-15.51682769760369</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.91035156905279</v>
       </c>
       <c r="E67">
-        <v>-28.44717840789561</v>
+        <v>-27.50397878463001</v>
       </c>
       <c r="F67">
-        <v>-2.512987687526465</v>
+        <v>-2.554980944643983</v>
       </c>
       <c r="G67">
-        <v>-15.74153925244557</v>
+        <v>-15.65008543192321</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.04250236691601</v>
       </c>
       <c r="E68">
-        <v>-27.24280810318564</v>
+        <v>-27.71342976443278</v>
       </c>
       <c r="F68">
-        <v>-2.577863765778916</v>
+        <v>-2.603591200575063</v>
       </c>
       <c r="G68">
-        <v>-15.77020361099735</v>
+        <v>-15.58567545791115</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.09334988945842</v>
       </c>
       <c r="E69">
-        <v>-27.12393566048429</v>
+        <v>-27.35036841781582</v>
       </c>
       <c r="F69">
-        <v>-2.513185667335733</v>
+        <v>-2.555564115295553</v>
       </c>
       <c r="G69">
-        <v>-15.31712565903824</v>
+        <v>-15.21545715025445</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.05277709261211</v>
       </c>
       <c r="E70">
-        <v>-27.69233160403104</v>
+        <v>-27.19238807358423</v>
       </c>
       <c r="F70">
-        <v>-2.810610983310896</v>
+        <v>-2.446961006951524</v>
       </c>
       <c r="G70">
-        <v>-15.22889465459835</v>
+        <v>-15.18047130499543</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.92414163366484</v>
       </c>
       <c r="E71">
-        <v>-27.57729025034018</v>
+        <v>-27.79354752657648</v>
       </c>
       <c r="F71">
-        <v>-2.517218988219964</v>
+        <v>-2.496852747254735</v>
       </c>
       <c r="G71">
-        <v>-15.14985869039379</v>
+        <v>-15.28311807998607</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.70239126566599</v>
       </c>
       <c r="E72">
-        <v>-26.43751409887562</v>
+        <v>-27.23948873173801</v>
       </c>
       <c r="F72">
-        <v>-3.131307624732905</v>
+        <v>-2.611874046235656</v>
       </c>
       <c r="G72">
-        <v>-14.76488528126856</v>
+        <v>-15.38420558802772</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.39354742687695</v>
       </c>
       <c r="E73">
-        <v>-28.18310497461232</v>
+        <v>-27.83266901352875</v>
       </c>
       <c r="F73">
-        <v>-2.658871470833485</v>
+        <v>-2.926367872545502</v>
       </c>
       <c r="G73">
-        <v>-15.20307736521034</v>
+        <v>-14.99932818472313</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.00109314589516</v>
       </c>
       <c r="E74">
-        <v>-28.01589107187909</v>
+        <v>-27.66162855025904</v>
       </c>
       <c r="F74">
-        <v>-2.679778635712742</v>
+        <v>-2.849706611253422</v>
       </c>
       <c r="G74">
-        <v>-14.61271605555596</v>
+        <v>-15.02955677604221</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.53763231910894</v>
       </c>
       <c r="E75">
-        <v>-28.18363933454522</v>
+        <v>-28.36288539271683</v>
       </c>
       <c r="F75">
-        <v>-2.835949085427727</v>
+        <v>-2.845959077123156</v>
       </c>
       <c r="G75">
-        <v>-14.65965131493898</v>
+        <v>-15.0270606247056</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.01612106465582</v>
       </c>
       <c r="E76">
-        <v>-28.03813946467877</v>
+        <v>-28.17987164417084</v>
       </c>
       <c r="F76">
-        <v>-3.017397166439139</v>
+        <v>-2.890249397048638</v>
       </c>
       <c r="G76">
-        <v>-14.4465564643944</v>
+        <v>-14.86868909192518</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.44709616207046</v>
       </c>
       <c r="E77">
-        <v>-27.83095272187984</v>
+        <v>-28.12244606527957</v>
       </c>
       <c r="F77">
-        <v>-2.775339927667096</v>
+        <v>-2.8268867460411</v>
       </c>
       <c r="G77">
-        <v>-14.94795182849918</v>
+        <v>-14.66728377767977</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.841375705300869</v>
       </c>
       <c r="E78">
-        <v>-27.37750303406978</v>
+        <v>-28.60643578179736</v>
       </c>
       <c r="F78">
-        <v>-3.145602761003016</v>
+        <v>-3.026910137692889</v>
       </c>
       <c r="G78">
-        <v>-13.67296308023244</v>
+        <v>-14.41155075586215</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.206718468888178</v>
       </c>
       <c r="E79">
-        <v>-28.82383423348359</v>
+        <v>-28.75288663120542</v>
       </c>
       <c r="F79">
-        <v>-3.116080575134645</v>
+        <v>-3.092390924149384</v>
       </c>
       <c r="G79">
-        <v>-13.59808681649797</v>
+        <v>-14.20985245833651</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.561529324132469</v>
       </c>
       <c r="E80">
-        <v>-28.2365228540068</v>
+        <v>-29.51138112088316</v>
       </c>
       <c r="F80">
-        <v>-2.992165095349866</v>
+        <v>-3.293820055283723</v>
       </c>
       <c r="G80">
-        <v>-14.20201308649952</v>
+        <v>-14.51182883551944</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.913686614754889</v>
       </c>
       <c r="E81">
-        <v>-28.59647766745449</v>
+        <v>-29.26516119637511</v>
       </c>
       <c r="F81">
-        <v>-3.058333426750685</v>
+        <v>-3.295593589893117</v>
       </c>
       <c r="G81">
-        <v>-13.59997051690982</v>
+        <v>-14.2369409972116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.272436142365565</v>
       </c>
       <c r="E82">
-        <v>-30.28101792085678</v>
+        <v>-29.51769607788686</v>
       </c>
       <c r="F82">
-        <v>-3.397349413285605</v>
+        <v>-3.292316568447642</v>
       </c>
       <c r="G82">
-        <v>-13.70555705633933</v>
+        <v>-14.28522695917464</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.640295168061009</v>
       </c>
       <c r="E83">
-        <v>-30.45557474419344</v>
+        <v>-29.9952870606318</v>
       </c>
       <c r="F83">
-        <v>-3.244944721783747</v>
+        <v>-3.299741225478934</v>
       </c>
       <c r="G83">
-        <v>-13.61091352518988</v>
+        <v>-13.92873582859653</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.029063655797932</v>
       </c>
       <c r="E84">
-        <v>-30.27331045809572</v>
+        <v>-31.05220798741502</v>
       </c>
       <c r="F84">
-        <v>-3.738259047703325</v>
+        <v>-3.586767217079351</v>
       </c>
       <c r="G84">
-        <v>-13.05618361717467</v>
+        <v>-14.08257191398815</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.443431535372635</v>
       </c>
       <c r="E85">
-        <v>-31.24639574557494</v>
+        <v>-31.524502919808</v>
       </c>
       <c r="F85">
-        <v>-3.525966706448673</v>
+        <v>-3.493146789949757</v>
       </c>
       <c r="G85">
-        <v>-12.70330925759821</v>
+        <v>-13.87555522505368</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.88582556061173</v>
       </c>
       <c r="E86">
-        <v>-32.47536472109457</v>
+        <v>-31.72038885572079</v>
       </c>
       <c r="F86">
-        <v>-3.673189959846021</v>
+        <v>-3.659232797476252</v>
       </c>
       <c r="G86">
-        <v>-13.76012312319037</v>
+        <v>-13.56803368409247</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.356566738308052</v>
       </c>
       <c r="E87">
-        <v>-32.8149119664267</v>
+        <v>-32.2797278512522</v>
       </c>
       <c r="F87">
-        <v>-3.740456706422952</v>
+        <v>-3.595187571728808</v>
       </c>
       <c r="G87">
-        <v>-13.70978793353852</v>
+        <v>-13.67777495817377</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.859219987949425</v>
       </c>
       <c r="E88">
-        <v>-33.63345175720915</v>
+        <v>-33.0716673857136</v>
       </c>
       <c r="F88">
-        <v>-3.794452178839632</v>
+        <v>-4.107869955893242</v>
       </c>
       <c r="G88">
-        <v>-13.51818514463489</v>
+        <v>-13.99193248766845</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.401345580751534</v>
       </c>
       <c r="E89">
-        <v>-35.44279222578882</v>
+        <v>-34.43674191177077</v>
       </c>
       <c r="F89">
-        <v>-3.611435169967318</v>
+        <v>-3.999272646121033</v>
       </c>
       <c r="G89">
-        <v>-13.22365087382424</v>
+        <v>-13.81070329321212</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.986210967045167</v>
       </c>
       <c r="E90">
-        <v>-36.25831605288216</v>
+        <v>-34.81995723195886</v>
       </c>
       <c r="F90">
-        <v>-4.057562375153825</v>
+        <v>-4.002692975127192</v>
       </c>
       <c r="G90">
-        <v>-13.14651847330476</v>
+        <v>-14.10595429713202</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.620554588056334</v>
       </c>
       <c r="E91">
-        <v>-36.03876657604228</v>
+        <v>-36.35708659946346</v>
       </c>
       <c r="F91">
-        <v>-3.713990367903508</v>
+        <v>-4.124907816634022</v>
       </c>
       <c r="G91">
-        <v>-12.83208285798479</v>
+        <v>-13.99562374594473</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.310004417458309</v>
       </c>
       <c r="E92">
-        <v>-37.29625814509923</v>
+        <v>-36.72583570943404</v>
       </c>
       <c r="F92">
-        <v>-4.239558835385891</v>
+        <v>-4.342701345810665</v>
       </c>
       <c r="G92">
-        <v>-14.07814405932938</v>
+        <v>-14.12751753550207</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.06995588301721</v>
       </c>
       <c r="E93">
-        <v>-39.05642391442962</v>
+        <v>-38.73845031927003</v>
       </c>
       <c r="F93">
-        <v>-3.865773783853267</v>
+        <v>-4.374536333467653</v>
       </c>
       <c r="G93">
-        <v>-13.30790425779869</v>
+        <v>-14.23877503944035</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.907416112224553</v>
       </c>
       <c r="E94">
-        <v>-39.01303660496212</v>
+        <v>-39.66337754991467</v>
       </c>
       <c r="F94">
-        <v>-4.324116923128859</v>
+        <v>-4.516155681385063</v>
       </c>
       <c r="G94">
-        <v>-14.0238527677581</v>
+        <v>-14.6095577951115</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.830651869936399</v>
       </c>
       <c r="E95">
-        <v>-41.1874762334622</v>
+        <v>-40.7845348804967</v>
       </c>
       <c r="F95">
-        <v>-4.29864048365576</v>
+        <v>-4.702438114559213</v>
       </c>
       <c r="G95">
-        <v>-13.96409907604702</v>
+        <v>-14.10563317421471</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.84834645674161</v>
       </c>
       <c r="E96">
-        <v>-42.25124647718202</v>
+        <v>-42.07636360371681</v>
       </c>
       <c r="F96">
-        <v>-5.060433655027075</v>
+        <v>-4.918462250963476</v>
       </c>
       <c r="G96">
-        <v>-14.26307278842583</v>
+        <v>-14.8762652753918</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.959755755529786</v>
       </c>
       <c r="E97">
-        <v>-43.83119256642915</v>
+        <v>-43.5307803934713</v>
       </c>
       <c r="F97">
-        <v>-4.738729718843262</v>
+        <v>-5.034347537145516</v>
       </c>
       <c r="G97">
-        <v>-13.91589753299523</v>
+        <v>-14.8870642749409</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.174812366697425</v>
       </c>
       <c r="E98">
-        <v>-44.87930334703044</v>
+        <v>-44.6401750128184</v>
       </c>
       <c r="F98">
-        <v>-4.871690142299207</v>
+        <v>-5.163124705217323</v>
       </c>
       <c r="G98">
-        <v>-14.73187583169649</v>
+        <v>-15.18176241775575</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.471290999195095</v>
       </c>
       <c r="E99">
-        <v>-47.6672017639276</v>
+        <v>-45.97917684977642</v>
       </c>
       <c r="F99">
-        <v>-4.492381536924716</v>
+        <v>-5.197829157557609</v>
       </c>
       <c r="G99">
-        <v>-14.71222277810261</v>
+        <v>-15.52302172830767</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.866380135460857</v>
       </c>
       <c r="E100">
-        <v>-49.06484507504794</v>
+        <v>-47.73105551167276</v>
       </c>
       <c r="F100">
-        <v>-5.236463384856775</v>
+        <v>-5.674398036429595</v>
       </c>
       <c r="G100">
-        <v>-14.62890793378854</v>
+        <v>-15.48193951343808</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.304660234242708</v>
       </c>
       <c r="E101">
-        <v>-50.75980308290487</v>
+        <v>-49.62581658545911</v>
       </c>
       <c r="F101">
-        <v>-5.450144898245922</v>
+        <v>-5.566573593444198</v>
       </c>
       <c r="G101">
-        <v>-14.69483579293035</v>
+        <v>-15.88473689974675</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.84073162016852</v>
       </c>
       <c r="E102">
-        <v>-51.55735679301727</v>
+        <v>-51.26745520823123</v>
       </c>
       <c r="F102">
-        <v>-5.736097325692311</v>
+        <v>-5.863515142856126</v>
       </c>
       <c r="G102">
-        <v>-14.76281950085206</v>
+        <v>-16.32284787532282</v>
       </c>
     </row>
   </sheetData>
